--- a/downloads/korrigierte_referenz/Zoo_3NF.xlsx
+++ b/downloads/korrigierte_referenz/Zoo_3NF.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE_TIER" sheetId="1" r:id="Rdaf2185d9163404c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PFLEGER" sheetId="2" r:id="R4aff6941f57d4972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE" sheetId="3" r:id="R37ed3302d0f34802"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BEREICH" sheetId="4" r:id="R3e24e7d48b0d4885"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE_TIER" sheetId="1" r:id="Rbf91108e0b584e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PFLEGER" sheetId="2" r:id="R476a3a4ed966405c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE" sheetId="3" r:id="Rce6346be601c4a89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BEREICH" sheetId="4" r:id="Rb6bb747488c94f27"/>
   </x:sheets>
 </x:workbook>
 </file>
